--- a/docs/records/펌웨어-프로젝트-요구사항.xlsx
+++ b/docs/records/펌웨어-프로젝트-요구사항.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\stm32-baseboard\docs\records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F302BF-1B62-43DD-BD60-B805B2B7DC26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FA480E-AC11-4E35-A582-E90CB683D7E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14610" windowHeight="14280" activeTab="3" xr2:uid="{E5EDD162-4478-4810-936B-B88F765943DE}"/>
   </bookViews>
@@ -1319,25 +1319,30 @@
     <t>FW-REQ-019, FW-REQ-047, FW-REQ-052</t>
   </si>
   <si>
-    <t>다음 구현 대상으로 USART2(PA2/PA3)-ST-LINK Virtual COM Port를 사용한 PC START 명령 수신을 선정했다.</t>
-  </si>
-  <si>
-    <t>아직 구현·시험하지 않음.</t>
-  </si>
-  <si>
-    <t>UM1724 7.8 USART communication; 사용자 지시 (2026-08-28)</t>
-  </si>
-  <si>
-    <t>예정</t>
-  </si>
-  <si>
-    <t>USART2 초기화, READY 응답, START 수신 후 IDLE→AUTO 전이 구현·시험</t>
-  </si>
-  <si>
     <t>FW-DEV-007 USART2 기반 PC START 명령 수신을 다음 구현 작업으로 기록</t>
   </si>
   <si>
     <t>사용자 지시·Codex 기록</t>
+  </si>
+  <si>
+    <t>usart2_pins_init()에 RCC-&gt;APB1ENR |= RCC_APB1ENR_USART2EN;를 작성하여 USART2 클록 enable bit 17을 설정했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 코드 작성 확인. 빌드·다운로드·레지스터 관찰은 아직 수행하지 않았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>firmware/automation_controller/Src/main.c:47; 사용자 수행 (2026-08-28)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행 중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA2/PA3 MODER·AF7 설정 코드 분석 후 Clean Build 및 RCC_APB1ENR USART2EN(bit 17) 관찰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2692,10 +2697,10 @@
         <v>46262</v>
       </c>
       <c r="C19" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D19" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E19" t="s">
         <v>305</v>
@@ -4521,19 +4526,19 @@
         <v>409</v>
       </c>
       <c r="F11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
